--- a/base_prov_co/farmatodo/farmatodo_abbott_2026_09_29.xlsx
+++ b/base_prov_co/farmatodo/farmatodo_abbott_2026_09_29.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Farmatodo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Farmatodo'!$A$1:$Q$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Farmatodo'!$A$1:$R$63</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q63"/>
+  <dimension ref="A1:R63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -471,65 +471,70 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>MARCA</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>categoría</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>seller</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>ventas</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>valoración</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>reviews</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>img_count</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>video_count</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>title_count_characters</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>count_character_desc</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>url_imagen</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>url_producto</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>disponibilidad</t>
         </is>
@@ -556,56 +561,60 @@
           <t>8427030008608</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>4.9</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>76</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>6</v>
       </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>57</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>614</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Ensure está formulado para adultos que requieren recuperar su estado nutricional al pasar por una condición médica. Está específicamente diseñado para proveerlos nutrientes necesarios para apoyar una correcta alimentación. Contiene una combinación de macro y micronutrientes (28 vitaminas y minerales, proteínas, fibras, carbohidratos y ácidos grasos). Ademas, aporta fibra (FOS) que actúa a nivel intestinal, está formulado con antioxidantes y vitaminas (C,E y Selenio) y no contiene grasas trans.
 Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/t8Jzp77X2WzRxbmHs1eozYPs5FLUKfuCEbgHszkl8zVWcJoLwTr7NT70f5vkVBC04koZZOLM4eMH6ZTRHgfKmLXIpJ4ph3VTK1S5MYIf4jX81ews=s360-rw</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1050596-ensure-advance-vainilla</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -632,55 +641,59 @@
           <t>8710428018670</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>6</v>
       </c>
-      <c r="K3" t="n">
-        <v>0</v>
-      </c>
       <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" t="n">
         <v>67</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>114</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/0_AI5tk75G6mK4visr8C1FpDG7ovasazCaIpjw7XBtbdSgnoixtNtF6zPxepDfXFeX5zvXB7StU6QwTqO9rGZw5kf4Dui37KmBq7GH76DZOw_4Z1pw=s360-rw</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/232300088-ensure-advance-rpb-sabor</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -707,56 +720,60 @@
           <t>7703186033031</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>6</v>
       </c>
-      <c r="K4" t="n">
-        <v>0</v>
-      </c>
       <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>77</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>499</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Ensure Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.
 Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/-ebsasjD6ZLLvc2w268NgcYskLHOuBTH-YkwBtYwemNcNmg5YJGZ_3lzXlW8FduAAc46PnP2b5wmWHr3wpTn6mQnAvEYddLygQPK28EQxG_u7Nsr=s360-rw</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/233000052-ensure-advance-rpb-sabor</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -783,56 +800,60 @@
           <t>8427030008592</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>6</v>
       </c>
-      <c r="K5" t="n">
-        <v>0</v>
-      </c>
       <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
         <v>56</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>499</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Ensure Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.
 Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/4O8yfN1jecVWayzbzcfpkxK5eZpNAbXCh6UF0G53hwGa51C_vGWFVbtUxhhVMjGTCxoMw-I8XEiX5qpNlA-u_iTst3aK3aVyek7RrhTSGJxZ_rU-nQ=s360-rw</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1043564-ensure-advance-vainilla</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -859,56 +880,60 @@
           <t>8710428018717</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>6</v>
       </c>
-      <c r="K6" t="n">
-        <v>0</v>
-      </c>
       <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
         <v>56</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>499</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Ensure Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.
 Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/qfwAGNKzLRmYYr66fUVczRavtA-bZ-pSaOUcCYI5PYLPNxR8RZApYl4fKn6j_qS_k0B-osiwTjq1KLLtRb5NuYdcwvx5im4jE7_xWPAfUDiM1KeT=s360-rw</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/232350085-ensure-advance-rpb-sabor</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -935,56 +960,60 @@
           <t>8710428013859</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="J7" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>6</v>
       </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
       <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
         <v>54</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>614</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Ensure está formulado para adultos que requieren recuperar su estado nutricional al pasar por una condición médica. Está específicamente diseñado para proveerlos nutrientes necesarios para apoyar una correcta alimentación. Contiene una combinación de macro y micronutrientes (28 vitaminas y minerales, proteínas, fibras, carbohidratos y ácidos grasos). Ademas, aporta fibra (FOS) que actúa a nivel intestinal, está formulado con antioxidantes y vitaminas (C,E y Selenio) y no contiene grasas trans.
 Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/mOsezleQcN_oqPJXGh4eGTTmRNnx9SsbiVMpjzn2cqcLXe9Qsxl3FJIxNZXjebqUzeorFvmiiC22-1TRImgkWHG6ZamrvGPi6ZSmmzC6w8MKGvWp=s360-rw</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/106461753-ensure-advance-fresa</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1011,47 +1040,49 @@
           <t>7703186998262</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="K8" t="n">
-        <v>0</v>
-      </c>
       <c r="L8" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" t="n">
         <v>76</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>616</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Complemento nutricional para adultos, con Hmb, vitaminas y minerales. Para personas que requieran recuperar o mantener su masa corporal magra. Alimento en polvo para propósitos médicos especiales, polimérico, a base de maltodextrina, proteína, Hmb, vitaminas y minerales para adultos y adultos mayores que requieren recuperar mantener su masa corporal magra. Modo de uso Instrucciones de uso para preparar una porción de 230 ml, vierta 190ml de agua fría o a temperatura ambiente en un vaso y adicione gradualmente 6 mededas rasas cuchara medidora incluida ó 54.1g de Ensure Advance polvo. Agite hasta disolver el po</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/Z0iklNq6OEbHkmkLoUaywrL_nnphhsMg9PDboJQk-wdg22F5akPWJEWPaZxD26T6Ud7Tn1UFrWOYZG-mc275jk7X0_AtdtR4GgM4m65MFqa9WVI=s360-rw</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/238000246-ensure-advance-400-gr-ensure-advance-liquido-sabor-vainilla-oferta-x-2-und</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1078,56 +1109,60 @@
           <t>8710428018694</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>6</v>
       </c>
-      <c r="K9" t="n">
-        <v>0</v>
-      </c>
       <c r="L9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" t="n">
         <v>67</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>499</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Ensure Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.
 Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/J5du7T8gJIu4fd6qPsXHQIDMRSHLT6BfyMoXdmjmwTrlqyqnWNEDDSZo_1m7vgyR3kLNhZWxsBzNfiWPA9kXDXzLLXx_egIbqKeVkLIZFdrbtV4=s360-rw</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/232350077-ensure-advance-rpb-sabor</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1154,56 +1189,60 @@
           <t>8427030003153</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>6</v>
       </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
       <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
         <v>48</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>620</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Ensure está formulado para adultos que requieren recuperar su estado nutricional al pasar por una condición médica. Está específicamente diseñado para proveerlos nutrientes necesarios para apoyar una correcta alimentación. Contiene una combinación de macro y micronutrientes (28 vitaminas y minerales, proteínas, fibras, carbohidratos y ácidos grasos). Ademas, aporta fibra (FOS) que actúa a nivel intestinal, está formulado con antioxidantes y vitaminas (C,E y Selenio) y no contiene grasas trans.
 Nutrición especializada para adultos: contiene proteína, vitaminas y minerales para complementar tu alimentación diaria.</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/KpUwD44x79aXzeo5l-00O1cOZhoLv9CA-3g4EVDOlFNfqzfDrlZM0hfH0iQGJgdii_qfdORQUxBpXGVGbxZwL2UAZjo8wGFfK1Joae-PBUp05Ac=s360-rw</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1017009-ensure-vainilla-x400g</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1230,56 +1269,60 @@
           <t>8710428019561</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>6</v>
       </c>
-      <c r="K11" t="n">
-        <v>0</v>
-      </c>
       <c r="L11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" t="n">
         <v>46</v>
       </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
         <v>620</v>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Ensure está formulado para adultos que requieren recuperar su estado nutricional al pasar por una condición médica. Está específicamente diseñado para proveerlos nutrientes necesarios para apoyar una correcta alimentación. Contiene una combinación de macro y micronutrientes (28 vitaminas y minerales, proteínas, fibras, carbohidratos y ácidos grasos). Ademas, aporta fibra (FOS) que actúa a nivel intestinal, está formulado con antioxidantes y vitaminas (C,E y Selenio) y no contiene grasas trans.
 Nutrición especializada para adultos: contiene proteína, vitaminas y minerales para complementar tu alimentación diaria.</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/oy7geihxMLCI2QLrtp_crhdqGG2f-sim7q6Aj7-PuLUnEIPfxcLmSXDW7SoLiXXnX43Hu2tjvfwsV94x5oIoR9SD1cp4k3-9yQLf85iXNRqYsfYH=s360-rw</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/237850038-ensure-sabor-vainilla</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1306,56 +1349,60 @@
           <t>7703186031433</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>6</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
       <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="n">
         <v>55</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>531</v>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Ensure Clinical es un alimento para propositos medicos especialespara adultosque presenten sarcopenia o caquexia asociada a desnutrición proteico-calórica moderada o severa asociada a una condición médica. Aporta 1,5 Kcal/ml y está formulado con HMB, 28 vitaminas y minerales para apoyar su alimentación en adultos con una perdida mayor en masa muscular y que no logran suplir sus requerimientos nutricionales con una alimentación normal o modificada.
 Contiene HMB, calcio y vitamina D3, nutrientes clave para el soporte muscular.</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/Rpe_YcH6Diwwn4aLCOo5MfLnsiNUqjo4cHbRMXBFgYzUDYzfJRe5aS5Uv8-ImUIv7jFlNcuXIlX3-ebfvuIY-AYRqDPhG1yTAofRGlUBn49ymdQ=s360-rw</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/211200192-ensure-clinical-rpb-x-220-ml</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1382,56 +1429,60 @@
           <t>8710428018861</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="K13" t="n">
         <v>6</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
       <c r="L13" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" t="n">
         <v>63</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>520</v>
       </c>
-      <c r="N13" t="inlineStr">
+      <c r="O13" t="inlineStr">
         <is>
           <t>Ensure Advance es un alimento para propositos medicos especiales, dirigido adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.Formulado con CaHMB y proteína para apoyar los músculos, así como 28 vitaminas y minerales, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.
 Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr">
+      <c r="P13" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/n6KuqQOumNI_aZAvmVgS4ExjWYWtBIfAwxlzY2VQN4M0_7ZczRWXVDuRNM94gAuacn4rVK_fk4C2K8WTnSchbvbQVN_PrG72MriB0PO6iXy7QEYe7g=s360-rw</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/237850046-ensure-advance-sabor</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr">
+      <c r="R13" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1458,48 +1509,50 @@
           <t>7703186341334</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
         <v>5</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
       <c r="L14" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" t="n">
         <v>52</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>525</v>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>Ensure Advance Cafe es un alimento para propositos medicos especiales, dirigido adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.Formulado con CaHMB y proteína para apoyar los músculos, así como 28 vitaminas y minerales, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.
 Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/GBWY1wB9vq2AiHrj3mACrgs0RYERxnfxNlK0BsnVDyjg2XAW0EztmNXEC1B1ss4YEJGkU9CVS1f-WblimX37J7BRPo81PGRRE9dC9wtQdl8poSX2iQ=s360-rw</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/239100214-ensure-advance-cafe-lata-x-400-gr</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1526,56 +1579,60 @@
           <t>8710428011848</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>ENSURE</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>6</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
       <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
         <v>58</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>499</v>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>Ensure Advance es ideal para adultos que requieran mantener o recuperar su masa muscular perdida por una condición de salud, y volver a llevar un estilo de vida activo.Formulado con CaHMB y proteína para los músculos, así como 28 vitaminas y minerales, incluyendo calcio y vitamina D, que apoyan la vitalidad fuerza y energía. También contiene omega 3 y 6 y no contiene grasas trans.
 Contiene HMB (beta-hidroxi-beta-metilbutirato), un nutriente que ayuda a preservar y reconstruir la masa muscular.</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/CCGB9PI4tbNtuMBk8YvmZT2kFUBvcpBG22iTE-ssQ76BuP_cnSw7x0YmTZa63Zro9YWN4mlUdsCE3lrSGpFzqIyjojcPDzsqPeejD2Ju4vbOJK8=s360-rw</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/206650228-ensure-advance-chocolate</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1602,56 +1659,60 @@
           <t>8710428017987</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>2</v>
       </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
       <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="n">
         <v>39</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>595</v>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>Ensure Plus HN alimento para propositos medicos especiales, diseñada para adultos que están en riesgo nutricional o que experimentan pérdida de peso involuntaria asociada a una condición de salud. Es una fórmula nutricional alta en calorías (1.5 kcal/ml), que contiene una combinación de proteínas, 28 vitaminas y minerales, y un balance adecuado de ácidos grasos omega 3 y omega 6. Es ideal para ayudarte a mejorar tu estado nutricional y contribuir a una ganancia de masa corporal adecuada.
 Aporta 14?g de proteína por porción (220?ml), ideal para apoyar el mantenimiento de la masa muscular.</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/w-qOAc0LGQcHntzRhdezMut9K7oLHg0ibNWBmLbI8ZBRtPvq1PQyTGyP4Ak6tqtowv_sZIOIPeajL_XO0ujr5-QQl2EmP-kcPZ6TsRXEIWmxJZw2=s360-rw</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/229350210-ensure-plus-rpb-hn-x220ml</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1678,56 +1739,60 @@
           <t>7703186069917</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>2</v>
       </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
       <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="n">
         <v>63</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>467</v>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>Pulmocare Vainilla 237 mL es un alimento para propósitos médicos especiales formulado para personas con enfermedades respiratorias crónicas como EPOC, insuficiencia respiratoria, fibrosis pulmonar, fibrosis quística o enfisema pulmonar. Su fórmula hipercalórica y nutricionalmente completa ayuda a cubrir las necesidades energéticas y nutricionales cuando la alimentación habitual no es suficiente
 Nutrición especializada para personas con enfermedades respiratorias</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/gqt7zmQ4sfoUV0260qBBFSNzzSWul4VJHk1hh49a8G4_wI0V3pcOCYSzj9Sgamj1jhnr30lT6gp7onwgePwi25VVhSS3sBhrloz404SVhxbirEcH=s360-rw</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1015930-pulmocare-x237ml</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1754,56 +1819,60 @@
           <t>8710428022790</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ESPECIALIZADOS</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>5</v>
       </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
       <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
         <v>62</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>444</v>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>ProSure Vainilla 220 mL es un alimento para propósitos médicos especiales, formulado para brindar soporte nutricional a adolescentes y adultos con desnutrición asociada a enfermedades oncológicas, pérdida involuntaria de peso o caquexia. Su fórmula hiperproteica contiene EPA y FOS, nutrientes que ayudan a complementar los requerimientos nutricionales cuando la alimentación habitual no es suficiente.
 Contiene 14,5 g de proteína por porción.</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/ym8TG6WxxQTd-s0PTjxGzxRf0glY1tk-FA94Lvt_ADp-5e73guXH4HWcU-xgtrx5Gg_B7hGJKboF5_NK5W4u_zRC7YBi8T6D6pjRze6dqMLcRE6A9w=s360-rw</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/211200379-alimento-liquido-prosure</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1830,56 +1899,60 @@
           <t>8427030008943</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>6</v>
       </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
       <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
         <v>59</v>
       </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
         <v>584</v>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.
 Aporta 11,1 g de proteína y 8,6 g de fibra por porción. Apoya el control glucémico y el funcionamiento digestivo.</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/Z00lSvFocl-r2Pd-UqCh5gBJoipeh7nUrTDJkZlsyo99fI3Zfu_KZgQIZS1htLJ-5KmddAvAmNJbgBsqTl0rozO7kztszsOM6XVAJFNdyj89JRAlNQ=s360-rw</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/283000464-glucerna-vainilla-850</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1906,56 +1979,60 @@
           <t>7703186030283</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J20" t="n">
+      <c r="K20" t="n">
         <v>6</v>
       </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
       <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
         <v>63</v>
       </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
         <v>581</v>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.
 Contiene 11 g de proteína y 8,8 g de fibra por porción para apoyar la saciedad, el metabolismo y la digestión.</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/COZtnpSO9XE0WddQprUHc7J0hBf8xSvAQFrlFmrEdDiSlVal0WcGnPEIVj273CWcWX4QvKnzP0K3i7NOS_yNk-SZ8lzGxpN3J48-t5Zmb0gPyu90=s360-rw</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1050402-glucerna-vainilla</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -1982,47 +2059,49 @@
           <t>7703186499844</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="n">
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
         <v>4</v>
       </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
       <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
         <v>48</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>610</v>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>Oferta Glucerna Vainilla 850 más Glucerna Vainilla 400gr con el 21 de descuento. Alimento con propósito medicos especiales con una mezcla de carbohidratos de digestión lenta, para personas con diabetes o hiperglicemia. Alimento en polvo para propósitos médicos especiales, polimérico e hiperproteico, a base de una mezcla de carbohidratos de digestión lenta para intervención nutricional por vía oral o sonda a adultos con diabetes tipo 2 o hiperglicemia. Modo de uso ? Oral / Sonda ? Administrar sólo bajo supervisión médica ? Para administración por sonda siga las recomendaciones del profesional de la salud</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/udy8wB0eEbibuq-V1f5T8tTlDVLNK6EW8vngZ5ZLqoj-yxKVfw79D3euSbLctoEVWZCzhETjHMVxlijTCDF_Su5LsI-ibZZWLJA68450FIgkn11R=s360-rw</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/243900265-glucerna-vainilla-oferta-850gr-400gr-x-2-latas</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2049,56 +2128,60 @@
           <t>7703186032737</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>6</v>
       </c>
-      <c r="K22" t="n">
-        <v>0</v>
-      </c>
       <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
         <v>84</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>581</v>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.
 Contiene 11 g de proteína y 8,8 g de fibra por porción para apoyar la saciedad, el metabolismo y la digestión.</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/0ZKOaxMHwV9DV_iWyZBdxokzmnzGOwAG7v8LjVbgI3ifIFzssQewaaZJRfHO2o9H1Lych2AX9iyvu80Y7tZD157Nn9eXECVLQuIkQIfY-o4k2u37rg=s360-rw</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/107611792-oft-glucerna-vainilla</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2125,47 +2208,49 @@
           <t>7703186190376</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="n">
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
         <v>4</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
       <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
         <v>52</v>
       </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
         <v>469</v>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/Jv10LxuFpvuVEStC7JBjbjw-yQFMctnqzGzz7J5OoJG5RdoXnL5x1TBiJaorzZaWYcUpzk2AasTrFWkm_cM4UakZVsDvLAUFPvMRyPtVpb0BwBE2=s360-rw</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/239150289-glucerna-liquido-sabor-vainilla-y-fresa-pack-x-8-und</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2192,56 +2277,60 @@
           <t>7703186031525</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>6</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
       <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>31</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>581</v>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.
 Contiene 11 g de proteína y 8,8 g de fibra por porción para apoyar la saciedad, el metabolismo y la digestión.</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/xlhbaatSuzOalVx6s4VHyNONxxU204xticq13epM4V59WUap5ZYrCaEQ5gzHE3ue6dwvS0om5NmKapg-VXMsx1tk8g7FVMlie5TM7-YAY_g4mwYa=s360-rw</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1052904-glucerna-fresa</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2268,55 +2357,59 @@
           <t>8427030008936</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>6</v>
       </c>
-      <c r="K25" t="n">
-        <v>0</v>
-      </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>32</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>469</v>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/hkw61HR6BY9z9RdQGIIGIu6t7VXAWAvwv8KrF5kbf0kjlAQbIp_Y-7EBgiKpvLq0_iJhiAw36kyml2RIYw110MN5CJbnNMJDRZGH93ZzR9Tt0oE=s360-rw</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1026565-glucerna-sr-vainilla</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2343,48 +2436,50 @@
           <t>8427030009346</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="n">
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
         <v>4</v>
       </c>
-      <c r="K26" t="n">
-        <v>0</v>
-      </c>
       <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
         <v>60</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>584</v>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.
 Aporta 11,1 g de proteína y 8,6 g de fibra por porción. Apoya el control glucémico y el funcionamiento digestivo.</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/u2jXytYeaQCd2NCItOk4IwUvpm8dpAkxK3YBnuoBeA6--QU-kMDJg-aUgMTJwI9nC4_0uE_g0lT9-jUoAJYkDQp8F3_r0KZelNt7D-iYUAeas6gz=s360-rw</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/243950238-glucerna-abbott-sabor-capuchino-lata-x-400-gr</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2411,48 +2506,50 @@
           <t>8710428024299</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>GLUCERNA</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="n">
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
         <v>6</v>
       </c>
-      <c r="K27" t="n">
-        <v>0</v>
-      </c>
       <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
         <v>69</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>581</v>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>Glucerna te ayuda a nivelar tus niveles de azúcar en 4 semanas gracias a su fórmula única con bajo índice glicémico, carbohidratos de lenta digestión y m-inositol compuestoque ayuda a respaldar el metabolismo, los nivenes de glucosa y la sensibilidad a la insulina. Glucerna es nutrición especializada para personas con diabetes tipo 2 o hiperglicemia, es alta en proteina, sin azucares añadidos y fuente de 28 vitaminas y minerales. Glucerna actúa desde el primer día.
 Contiene 11 g de proteína y 8,8 g de fibra por porción para apoyar la saciedad, el metabolismo y la digestión.</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/jN6-t0Np34GU1RjqVgQm7nc5hB5mg3K04c7G9BTNg6bVYJkGKOqyRumsef0MPtjT14V_Q41Ie7O7k1agaW9cNS4pCZYp1ORZi7kW1oVzcEysejod=s360-rw</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/211200256-glucerna-16-kcal-frasco</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2479,55 +2576,59 @@
           <t>7501033957376</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
       <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
         <v>87</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>144</v>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>ES UN MEDICAMENTO. NO EXCEDER SU CONSUMO. LEER INDICACIONES Y CONTRAINDICACIONES EN LA ETIQUETA. SI LOS SíNTOMAS PERSISTEN, CONSULTAR AL MÉDICO.</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/Yq2Aok4Fo_0fszI8lvm_IjRjKOpelIAanI7qEKUGF-NpIkia0PxSSWCtymAy9YK8sNWKVlTSyde1UvgjcOYkiY1tDkxe8hBaaUd8HzjjE9ZCEmf1=s360-rw</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1036529-pedialyte-zinc-suero</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2554,55 +2655,59 @@
           <t>7501033961557</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
       <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
         <v>88</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>144</v>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>ES UN MEDICAMENTO. NO EXCEDER SU CONSUMO. LEER INDICACIONES Y CONTRAINDICACIONES EN LA ETIQUETA. SI LOS SíNTOMAS PERSISTEN, CONSULTAR AL MÉDICO.</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/tXpTU8v4K-j20OgtfDhZyCzfUp3wjgt3sG9_JU11PV4J5YwNwbE10he6-3ixzgPq9dEVTYivoG8jXy-qzfUcVHX2f7lMGWdOfxAOvQsaImQQm8M=s360-rw</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/206650210-pedialyte-max-60-suero</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2629,55 +2734,59 @@
           <t>7501033957369</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="n">
-        <v>0</v>
-      </c>
       <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
         <v>91</v>
       </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
         <v>144</v>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>ES UN MEDICAMENTO. NO EXCEDER SU CONSUMO. LEER INDICACIONES Y CONTRAINDICACIONES EN LA ETIQUETA. SI LOS SíNTOMAS PERSISTEN, CONSULTAR AL MÉDICO.</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/OU2rmVTzxDP2iG_VZNc1Ar8COhn8odm8T2_Iu9nzEPHePKvD80G59f6y3zDKsfxF3tKsBzqajszSZzZBneew9Bway3bV-yEEohNiWtE0qB0_j7Vu=s360-rw</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1036528-pedialyte-zinc-suero</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2704,55 +2813,59 @@
           <t>7501033961540</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>37</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>1</v>
       </c>
-      <c r="K31" t="n">
-        <v>0</v>
-      </c>
       <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
         <v>86</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>144</v>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>ES UN MEDICAMENTO. NO EXCEDER SU CONSUMO. LEER INDICACIONES Y CONTRAINDICACIONES EN LA ETIQUETA. SI LOS SíNTOMAS PERSISTEN, CONSULTAR AL MÉDICO.</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/j73sDFq6J1NlVPv-_tJ7kmYQZBIGukf0ZW2q3c2dm3MWjanoTTmw-Jz9tWV4mFGmOrYot_76w8eyOXZeiwQRrrZPp5iBHEHO32_Zl1L6TgNWuOILUA=s360-rw</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/206650201-pedialyte-max-60-suero</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2779,55 +2892,59 @@
           <t>7501033959967</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>1</v>
       </c>
-      <c r="K32" t="n">
-        <v>0</v>
-      </c>
       <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
         <v>90</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>53</v>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>ESTE PRODUCTO REQUIERE FÓRMULA MÉDICA PARA SU COMPRA.</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/_h3Axzl-RNwHp7MwUgXJZo_5rI3cfAj_q8rpMBkac02RXBugUeWEpEsQdMH6FWGS6JQULrQVGP4bRcVNO2Jfg0ZQAvCauLZK8S3T8R3BIePIEzg=s360-rw</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1051669-pedialyte-zinc-suero</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2854,55 +2971,59 @@
           <t>7501033957413</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="K33" t="n">
-        <v>0</v>
-      </c>
       <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
         <v>89</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>144</v>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>ES UN MEDICAMENTO. NO EXCEDER SU CONSUMO. LEER INDICACIONES Y CONTRAINDICACIONES EN LA ETIQUETA. SI LOS SíNTOMAS PERSISTEN, CONSULTAR AL MÉDICO.</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/Wo54h-UGuwHXzZv9KHpB6sXG8Pmt6m5vYlPSOjwgrlT6M7fdSH60Ek_7I_2iU9U7dr-0dRmdnkoKzNRveNxnj7DK0REfo0iUg2LZPJnm1pcYbrS_=s360-rw</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1036531-pedialyte-zinc-suero</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -2929,55 +3050,59 @@
           <t>7501033959974</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
           <t>4.4</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J34" t="n">
+      <c r="K34" t="n">
         <v>1</v>
       </c>
-      <c r="K34" t="n">
-        <v>0</v>
-      </c>
       <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>91</v>
       </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
         <v>144</v>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>ES UN MEDICAMENTO. NO EXCEDER SU CONSUMO. LEER INDICACIONES Y CONTRAINDICACIONES EN LA ETIQUETA. SI LOS SíNTOMAS PERSISTEN, CONSULTAR AL MÉDICO.</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/CQVGs7biX6r8Nr9OfVNL6zXl2s8ksdMUiaUbn6RcFWablrrfy8GkEnJRu1Gj-2ReAe80jdG1-6plNA19TMnX_nZEQsYvOB2FkO7w3BNx-WtgI9NX=s360-rw</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1051671-pedialyte-zinc-suero</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3004,55 +3129,59 @@
           <t>7501033959981</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>PEDIALYTE</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J35" t="n">
+      <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="K35" t="n">
-        <v>0</v>
-      </c>
       <c r="L35" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" t="n">
         <v>91</v>
       </c>
-      <c r="M35" t="n">
+      <c r="N35" t="n">
         <v>144</v>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>ES UN MEDICAMENTO. NO EXCEDER SU CONSUMO. LEER INDICACIONES Y CONTRAINDICACIONES EN LA ETIQUETA. SI LOS SíNTOMAS PERSISTEN, CONSULTAR AL MÉDICO.</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/ig2KuSWDAHg3p7ASrCEZbgkMYoCudN7KWfHqsDZ_jO_6XkO5H5RnlRFUDEU27CMuNReHj0ttZkjCcdsZR8tjasIqNd3TU5Zu3ORBkVph9LHolTU=s360-rw</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1051672-pedialyte-zinc-suero</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3079,56 +3208,60 @@
           <t>8886451012074</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>8</v>
       </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
       <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
         <v>69</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>467</v>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>Complementa la nutrición de tu hijo con Pediasure, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.
 Contiene arginina (500 mg) y vitamina K2 (4 mcg) que apoyan el desarrollo de huesos fuertes y el crecimiento saludable.</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/fg2M7bbuJ-_jx5Awys05fkBkvB6iw0OOOJUGfsUEhx4rV15KWW_54XQuc-3RGuTEvdmY81AEXjBaYidinj4qYkShc0EIJWBeE_Cv9xXg9_nPozH2=s360-rw</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/224700241-pediasure-peptigro-vainilla-lata-x-850-gr</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3155,56 +3288,60 @@
           <t>8886451007049</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>8</v>
       </c>
-      <c r="K37" t="n">
-        <v>0</v>
-      </c>
       <c r="L37" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" t="n">
         <v>83</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>467</v>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>Complementa la nutrición de tu hijo con Pediasure, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.
 Contiene arginina (500 mg) y vitamina K2 (4 mcg) que apoyan el desarrollo de huesos fuertes y el crecimiento saludable.</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/Od0LMZNWmLbGTwfd1rciLwxjrzQuzkhGeD5YdWtjZdsoVHodBgw_793-exOcjsERWnoxt8mglGHpWUwtvDl2olNLQTfjgy0SmwL01nG6eu-P7SyIPQ=s360-rw</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/237700013-pediasure-ninos-sabor</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3231,48 +3368,50 @@
           <t>8886451012043</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" t="n">
         <v>8</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
       <c r="L38" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" t="n">
         <v>74</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>467</v>
       </c>
-      <c r="N38" t="inlineStr">
+      <c r="O38" t="inlineStr">
         <is>
           <t>Complementa la nutrición de tu hijo con Pediasure, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.
 Contiene arginina (500 mg) y vitamina K2 (4 mcg) que apoyan el desarrollo de huesos fuertes y el crecimiento saludable.</t>
         </is>
       </c>
-      <c r="O38" t="inlineStr">
+      <c r="P38" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/5Y2oC_UHPBn2hoBGr4EWRLaj5KwBDrWzPEvGCJe7A0kvXsb3rX3j1XD1x6LvnNIQgKfASkkdX7hnqPyurJx2UbeM8qokuQ3-DwA_XALIpcaO3xIs1Q=s360-rw</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/224700250-pediasure-peptigro-vainilla-lata-x-400-gr</t>
         </is>
       </c>
-      <c r="Q38" t="inlineStr">
+      <c r="R38" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3299,56 +3438,60 @@
           <t>8710428020185</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I39" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>8</v>
       </c>
-      <c r="K39" t="n">
-        <v>0</v>
-      </c>
       <c r="L39" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" t="n">
         <v>85</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>467</v>
       </c>
-      <c r="N39" t="inlineStr">
+      <c r="O39" t="inlineStr">
         <is>
           <t>Complementa la nutrición de tu hijo con Pediasure, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.
 Contiene arginina (500 mg) y vitamina K2 (4 mcg) que apoyan el desarrollo de huesos fuertes y el crecimiento saludable.</t>
         </is>
       </c>
-      <c r="O39" t="inlineStr">
+      <c r="P39" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/q72Vyue8ZSNU8Hoc1Lf67zKIsWwXIMYYJCk1mHGr6o78JK7LTha0HunxO4YJQQMJPLecWmN_3OIyYadMX_sOy32avlU8Nm7rh1ZwdQ8bd5Dcr-e4=s360-rw</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/237800057-pediasure-rpb-sabor</t>
         </is>
       </c>
-      <c r="Q39" t="inlineStr">
+      <c r="R39" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3375,56 +3518,60 @@
           <t>8710428020314</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I40" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>8</v>
       </c>
-      <c r="K40" t="n">
-        <v>0</v>
-      </c>
       <c r="L40" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" t="n">
         <v>81</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>467</v>
       </c>
-      <c r="N40" t="inlineStr">
+      <c r="O40" t="inlineStr">
         <is>
           <t>Complementa la nutrición de tu hijo con Pediasure, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.
 Contiene arginina (500 mg) y vitamina K2 (4 mcg) que apoyan el desarrollo de huesos fuertes y el crecimiento saludable.</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
+      <c r="P40" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/-L-Qn3oqLopbFCsN7h2sdbxF3upi7PIKFrFj6YYrfOvjnDv7P6mwz0YxIrTq9GJWRhn4mi-uukQoneuDjgjevbgLn5qlu46askbFBKPb26IS96z4=s360-rw</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/237850020-pediasure-rpb-sabor</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
+      <c r="R40" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3451,48 +3598,50 @@
           <t>8886451012036</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="n">
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
         <v>8</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" t="n">
         <v>71</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>467</v>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>Complementa la nutrición de tu hijo con Pediasure, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.
 Contiene arginina (500 mg) y vitamina K2 (4 mcg) que apoyan el desarrollo de huesos fuertes y el crecimiento saludable.</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/EDsIgJ2CTr-CPHl44TxKqufgu5_NOjeBnSIHSBlXgTqhngcEj4250p6_7P8VkjvWuxGeVQ-WtoP8IEmzZbDGCyKZjHOCJfz7w-Ywm1OftrYWI1YU_A=s360-rw</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/224650221-pediasure-peptigro-fresa-lata-x-850-gr</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3519,56 +3668,60 @@
           <t>8710428021885</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>5</v>
       </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
       <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
         <v>66</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>426</v>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>Apoya las necesidades nutricionales de tu adolescente con PediaSure 10+. Su fórmula especializada está diseñada para complementar la alimentación de adolescentes de 10 a 18 años que requieren apoyo nutricional especializado por una condición médica, déficit nutricional, riesgo nutricional o trastornos de la conducta alimentaria.
 Contiene arginina y vitamina K2, nutrientes que apoyan el crecimiento saludable de los huesos.</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/g06SnRkKIRNOpjTcGkO6P09bIQs8ygZPfVubAd8NSNIoz5F3eyjOR8wt3aJSYZ-UlzxWHB0UKh_ZJCTQGk8MuLXPKtJVcSR4_bOeJk85UaEftxo=s360-rw</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/235100241-pediasure-10-sabor-vainilla-lata-x-850-gr</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3595,49 +3748,51 @@
           <t>8886451012029</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="n">
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
         <v>5</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
       <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
         <v>66</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>432</v>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>Pediasure Peptigro Fresa 400gr Alimento con propósitos médicos especiales en polvo, polimérico, a base de maltodextrina, proteína, lípidos, vitaminas y minerales, para el manejo nutricional de nios de 2 a 13 años.
 Modo de uso:
 Para preparar una porción de 225mL servir en un vaso 190mL de agua fría o a temperatura ambiente y gradualmente añadir 5 meidas al ras aprox 48.6g de Pediasure Polvo. Agitar hasta disolver completamente.</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/-qHMEYy36DaMWko2_cxUs1Uxvr5_9w7oHDO-RCEVeUbEK49hEN3PSmVDCN7enb1_UE5ETIUHdLJFR57OZKwINc4bAzXSB7rn6zNgrUfvoUwonhwJ=s360-rw</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/224700233-pediasure-peptigro-fresa-lata-x-400-gr</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3664,56 +3819,60 @@
           <t>7703186033130</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
           <t>4.7</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="J44" t="n">
+      <c r="K44" t="n">
         <v>8</v>
       </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
       <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
         <v>90</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>467</v>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>Complementa la nutrición de tu hijo con Pediasure, que contiene los 5 grupos de nutrientes especiales: Proteínas, Carbohidratos, Vitaminas, Minerales y Lípidos. Pediasure ahora está mejorado con fosfopéptidos de caseína, que ayudan a la absorción de nutrientes, reforzado con Vitamina K2 y Arginina. Resultados visibles a partir de las 8 semanas.
 Contiene arginina (500 mg) y vitamina K2 (4 mcg) que apoyan el desarrollo de huesos fuertes y el crecimiento saludable.</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/0YpaVrbFWS5QP1OsMSiE6XFXJF-Dnj2QNk6HydqIteGEnri3OzA1zzrntMtvLQ8x3ngHAPWvMMfAnEv5mAIYIxWodi2GslAL-QhhHk3yzB8wuqcZ=s360-rw</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/239750129-pediasure-vainilla-rpb</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3740,56 +3899,60 @@
           <t>8710428024039</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>PEDIASURE</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J45" t="n">
+      <c r="K45" t="n">
         <v>5</v>
       </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
       <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
         <v>64</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>426</v>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>Apoya las necesidades nutricionales de tu adolescente con PediaSure 10+. Su fórmula especializada está diseñada para complementar la alimentación de adolescentes de 10 a 18 años que requieren apoyo nutricional especializado por una condición médica, déficit nutricional, riesgo nutricional o trastornos de la conducta alimentaria.
 Contiene arginina y vitamina K2, nutrientes que apoyan el crecimiento saludable de los huesos.</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/HqAyW9qojBEUw1m6ojpkPUYaEy_nLsLIwWJUoku8AH-iZ5XzOb8jpQic_5Hvihw1AtksFgsk6ybgj4RD_tHOfnzjpIW008c0bINFMvBrikzTWOxU2g=s360-rw</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/236750203-pediasure-liquido-upage-10-sabor-vainilla-frasco-x-220-ml</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3816,57 +3979,61 @@
           <t>5099864016987</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J46" t="n">
+      <c r="K46" t="n">
         <v>4</v>
       </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
       <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
         <v>62</v>
       </c>
-      <c r="M46" t="n">
+      <c r="N46" t="n">
         <v>554</v>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>La Fórmula Infantil Similac 1 con 5 HMO está diseñada para la alimentación de lactantes de 0 a 6 meses, cuando no es posible la lactancia materna o como complemento según indicación del profesional de salud.
 Su fórmula contiene 5 HMO (oligosacáridos estructuralmente similares a los presentes en la leche materna), además de nutrientes como hierro, DHA, luteína y nucleótidos, que participan en el desarrollo y crecimiento del bebé durante sus primeros meses de vida.
 Contiene hierro, nutriente importante para el crecimiento y desarrollo del lactante.</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/58NRiQs5cKJb7Gtp0PdIb_fVlYMtGS_6Gfg1APHNRn0t11i3KbpiGaLAyu7yytKRsABP8Ws8RXYaMEhO26pIX-CE-uxFi81CP7qlKuIJZLarGMQM=s360-rw</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264700107-formula-infantil-similac-1-5-hmo-0-6-meses-lata-x-350-gr</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3893,56 +4060,60 @@
           <t>5099864016994</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J47" t="n">
+      <c r="K47" t="n">
         <v>4</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
       <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
         <v>62</v>
       </c>
-      <c r="M47" t="n">
+      <c r="N47" t="n">
         <v>447</v>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>Esta fórmula infantil está desarrollada con base en nutrición científica para acompañar el desarrollo integral del bebé durante los primeros meses de vida. Su composición contribuye al apoyo de la salud intestinal y al proceso de maduración del sistema inmune.
 La presentación en lata de 800 gramos permite una preparación práctica dentro de la rutina diaria de alimentación del lactante, facilitando su almacenamiento y uso adecuado en el hogar.</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/jRfrj3NK_1nnb7KSu8jcNvlIg5j_vcq1xXpA3IG-C7m0I8om8YIeQP9-wUNDlmIKFLQqISIKDUM0V_G0d8Mh9fwpcu8Vth8goiHqKyzeoM9F43L_nQ=s360-rw</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264700115-formula-infantil-similac-1-5-hmo-0-6-meses-lata-x-800-gr</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -3969,57 +4140,61 @@
           <t>7703186863072</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
           <t>4.9</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J48" t="n">
+      <c r="K48" t="n">
         <v>2</v>
       </c>
-      <c r="K48" t="n">
-        <v>0</v>
-      </c>
       <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
         <v>63</v>
       </c>
-      <c r="M48" t="n">
+      <c r="N48" t="n">
         <v>476</v>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>Esta fórmula infantil está diseñada para acompañar la primera etapa de vida del bebé, brindando un apoyo nutricional durante el desarrollo inicial. Su composición busca integrarse dentro de la rutina de alimentación infantil, aportando nutrientes clave durante los primeros meses.
 La presentación en caja de 1400 gramos ofrece un formato familiar práctico para el uso continuo en el hogar, facilitando la preparación diaria dentro de la alimentación del lactante.
 Beneficios</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/vcI2HVoOsSB2hKfB1GXwlcwwSrPTopbg28mCazZo4NebSr3PZN6aua5rzg3Mzt2JN09N0bepZj2csh8glinDzFWh-x0xOtaQ0lapMHC8gkxnPXRM=s360-rw</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264700086-formula-infantil-similac-1-5-hmo-0-6-meses-caja-x-1400-gr</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4046,40 +4221,44 @@
           <t>7703186497345</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J49" t="n">
+      <c r="K49" t="n">
         <v>3</v>
       </c>
-      <c r="K49" t="n">
-        <v>0</v>
-      </c>
       <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
         <v>82</v>
       </c>
-      <c r="M49" t="n">
+      <c r="N49" t="n">
         <v>2151</v>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>Fórmula infantil líquida con hierro para lactantes de 0 a 6 meses con una combinación de grasas de fácil digestión, 5 HMOs (oligosacáridos), nucleótidos, DHA y luteína.
 Fórmula Infantil Similac 1 Líquida: Nutrición para los Primeros Meses
@@ -4106,17 +4285,17 @@
 Presentación lista para servir, sin necesidad de medir polvo o preparar una mezcla con agua. Contiene una combinación de 5 HMO u oligosacáridos. Aporta hierro, nucleótidos, DHA y luteína como parte de su composición nutricional incluye una combinación de grasas de fácil digestión</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/s2RmDUhJIZyHO37qgGaO3MJgUcTMeCWtELczvxKbdc3fYK0-2vs5HdswhUAvqcoenzm_0-1JuqOHSOWOgUi2s9yQCnSP8qIilYNJQrBVxlUqdQQ=s360-rw</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/278600465-formula-infantil-similac</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4143,57 +4322,61 @@
           <t>5099864017021</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
           <t>4.6</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J50" t="n">
+      <c r="K50" t="n">
         <v>4</v>
       </c>
-      <c r="K50" t="n">
-        <v>0</v>
-      </c>
       <c r="L50" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" t="n">
         <v>64</v>
       </c>
-      <c r="M50" t="n">
+      <c r="N50" t="n">
         <v>723</v>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>La Fórmula Infantil Similac 2 5 HMO está diseñada como alimento de continuación para bebés a partir de los 6 meses. Su formulación incluye hierro, una combinación de grasas de fácil digestión, 5 HMOs (oligosacáridos inspirados en la leche materna), nucleótidos, DHA y luteína.
 Esta fórmula infantil acompaña las necesidades nutricionales del bebé durante la etapa de crecimiento, contribuyendo al desarrollo integral dentro de la rutina de alimentación diaria. Su formato pequeño de 350 gramos es práctico para viajes, salidas o para probar la tolerancia del bebé a la fórmula.
 La presentación en lata facilita su almacenamiento y preparación, ofreciendo una opción conveniente para complementar la alimentación infantil.</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/3nKu48reaGc1v0vZlfEHmOCzQ9g_QGhhZNn2kc0rOcsUQrbFr8AZgN__IXYFY1KeedraOKLLaFCZUn59OV_9Wc9pQ0mSDgnyDS0N1C4hcPJ38ws=s360-rw</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264850076-formula-infantil-similac-2-6-meses-5hmo-lata-x-1800-gr</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4220,40 +4403,44 @@
           <t>7703186502186</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
           <t>3.8</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J51" t="n">
+      <c r="K51" t="n">
         <v>2</v>
       </c>
-      <c r="K51" t="n">
-        <v>0</v>
-      </c>
       <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
         <v>64</v>
       </c>
-      <c r="M51" t="n">
+      <c r="N51" t="n">
         <v>735</v>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>La Fórmula Infantil Similac 2 5 HMO está diseñada como alimento de continuación para bebés a partir de los 6 meses. Su formulación incluye hierro, una combinación de grasas de fácil digestión, 5 HMOs (oligosacáridos inspirados en la leche materna), nucleótidos, DHA y luteína.
 Esta fórmula infantil acompaña las necesidades nutricionales del bebé durante la etapa de crecimiento, contribuyendo al desarrollo integral dentro de la rutina de alimentación diaria. Su formato pequeño de 350 gramos es práctico para viajes, salidas o para probar la tolerancia del bebé a la fórmula.
@@ -4261,17 +4448,17 @@
 Beneficios</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="P51" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/dZAEcVTc_Sfsweyb0qCovtLWC4AVxSjTCc9iTe30ZsJDJhGKJF4vwnHxtXOd4CHqMfPzrRf8sMxY8a4qu8BIeg0UwowdpHqvXQPj_FnAL6x5LiCoVw=s360-rw</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264850050-formula-infantil-similac-2-6-meses-5-hmo-caja-x-1400-gr</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4298,40 +4485,44 @@
           <t>5099864017007</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
           <t>4.2</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="J52" t="n">
+      <c r="K52" t="n">
         <v>4</v>
       </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
       <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
         <v>63</v>
       </c>
-      <c r="M52" t="n">
+      <c r="N52" t="n">
         <v>735</v>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>La Fórmula Infantil Similac 2 5 HMO está diseñada como alimento de continuación para bebés a partir de los 6 meses. Su formulación incluye hierro, una combinación de grasas de fácil digestión, 5 HMOs (oligosacáridos inspirados en la leche materna), nucleótidos, DHA y luteína.
 Esta fórmula infantil acompaña las necesidades nutricionales del bebé durante la etapa de crecimiento, contribuyendo al desarrollo integral dentro de la rutina de alimentación diaria. Su formato pequeño de 350 gramos es práctico para viajes, salidas o para probar la tolerancia del bebé a la fórmula.
@@ -4339,17 +4530,17 @@
 Beneficios</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/tCtKapYL8b3kxhXcoAiF2xRvpIa__mo5qkmKGznr9std5ZnD9fWiqF6d2O5eIclzxHVbE2ffcm3Ky5Kq1mzTIoiRLzat_6OR4OfpIDWKqVCyhk4T=s360-rw</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264850092-formula-infantil-similac-2-6-meses-5-hmo-lata-x-350-gr</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4376,57 +4567,61 @@
           <t>5099864017229</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
+      <c r="J53" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J53" t="n">
+      <c r="K53" t="n">
         <v>8</v>
       </c>
-      <c r="K53" t="n">
-        <v>0</v>
-      </c>
       <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
         <v>74</v>
       </c>
-      <c r="M53" t="n">
+      <c r="N53" t="n">
         <v>652</v>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>A partir de los 2 años, los niños entran en una etapa llena de cambios, retos y mucho crecimiento. Similac 3 Kid está formulado para apoyar ese momento clave, combinando una mezcla única de grasas de fácil digestión con ingredientes como 5 HMOs, nucleótidos, DHA, luteína, hierro, calcio y vitamina D.
 Además, contiene probiótico y prebiótico, que junto con los 5 HMOs apoyan el buen funcionamiento del sistema inmune y gastrointestinal. Su fórmula está pensada para niños en crecimiento, ayudando a cubrir sus necesidades nutricionales mientras se preparan para nuevas etapas como el ingreso al jardín.
 Recomendado para niños a partir de los 2 años.</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/2rNnksy62WFuUZlf5Px9wwxBKg0hiGpFqoc93p_pczCiuupNDigTUFwht5JvESeKHaLz74ihJmT3__KV2a9RQvT-kvHQsfAsVlIuU2loXWTwVDJHOQ=s360-rw</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264800087-formula-infantil-similac-3-5-hmo-lata-x-1800-gr</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4453,57 +4648,61 @@
           <t>5099864017212</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J54" t="n">
+      <c r="K54" t="n">
         <v>8</v>
       </c>
-      <c r="K54" t="n">
-        <v>0</v>
-      </c>
       <c r="L54" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" t="n">
         <v>74</v>
       </c>
-      <c r="M54" t="n">
+      <c r="N54" t="n">
         <v>652</v>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>A partir de los 2 años, los niños entran en una etapa llena de cambios, retos y mucho crecimiento. Similac 3 Kid está formulado para apoyar ese momento clave, combinando una mezcla única de grasas de fácil digestión con ingredientes como 5 HMOs, nucleótidos, DHA, luteína, hierro, calcio y vitamina D.
 Además, contiene probiótico y prebiótico, que junto con los 5 HMOs apoyan el buen funcionamiento del sistema inmune y gastrointestinal. Su fórmula está pensada para niños en crecimiento, ayudando a cubrir sus necesidades nutricionales mientras se preparan para nuevas etapas como el ingreso al jardín.
 Recomendado para niños a partir de los 2 años.</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/dSYnjesHzUgfgrPy6e6ASwCV97_vkNzIwyElT1076zZ66f2qnJpDQmpSgSmWazA3pcpthIL-NSnbdws9mRigxJrgJrMbbyIGkVlyt8F7beaUO41c=s360-rw</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264850113-formula-infantil-similac-3-5-hmo-lata-x-800-gr</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4530,57 +4729,61 @@
           <t>5099864017205</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J55" t="n">
+      <c r="K55" t="n">
         <v>8</v>
       </c>
-      <c r="K55" t="n">
-        <v>0</v>
-      </c>
       <c r="L55" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" t="n">
         <v>73</v>
       </c>
-      <c r="M55" t="n">
+      <c r="N55" t="n">
         <v>652</v>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>A partir de los 2 años, los niños entran en una etapa llena de cambios, retos y mucho crecimiento. Similac 3 Kid está formulado para apoyar ese momento clave, combinando una mezcla única de grasas de fácil digestión con ingredientes como 5 HMOs, nucleótidos, DHA, luteína, hierro, calcio y vitamina D.
 Además, contiene probiótico y prebiótico, que junto con los 5 HMOs apoyan el buen funcionamiento del sistema inmune y gastrointestinal. Su fórmula está pensada para niños en crecimiento, ayudando a cubrir sus necesidades nutricionales mientras se preparan para nuevas etapas como el ingreso al jardín.
 Recomendado para niños a partir de los 2 años.</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/9dtSiGQeoBvHHAAtl7vTZz1FKWc6vhQsPuI7mNvOj4KQNdIKEk91yCTb62FIVvGtpa5bqluAv_kVg36n9NtNxKMfVMxg3bBGIlgpc_KltGd7cdsV=s360-rw</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/264800095-formula-infantil-similac-3-5-hmo-lata-x-350-gr</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4607,56 +4810,60 @@
           <t>7703186029508</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
           <t>4.8</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J56" t="n">
+      <c r="K56" t="n">
         <v>4</v>
       </c>
-      <c r="K56" t="n">
-        <v>0</v>
-      </c>
       <c r="L56" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" t="n">
         <v>68</v>
       </c>
-      <c r="M56" t="n">
+      <c r="N56" t="n">
         <v>464</v>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>Similac Mamá en polvo (400 gr) es un complemento nutricional especializado. Alimento a base de leche en polvo descremada, con vitaminas y minerales para mujeres embarazadas y en periodo de lactancia. Enriquecido con DHA, ácido fólico, hierro, calcio y prebióticos, apoya la salud materna y el óptimo desarrollo fetal y del lactante.
 Puede utilizarse durante la lactancia como parte de una alimentación equilibrada y de un programa de apoyo a la lactancia materna.</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/Da107bf_6lALPY1_N-VHZwClOt07aTAl8EFz1WNErozhMpwjAqEUuqXhJhK_0K8msFrjj1CfjyYK2avp9vtTgLrYsF7qZqh0aLXGO4CaMwWSHvFS=s360-rw</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1043377-leche-en-polvo-similac</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4683,55 +4890,59 @@
           <t>8427030003658</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
           <t>4.1</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J57" t="n">
+      <c r="K57" t="n">
         <v>3</v>
       </c>
-      <c r="K57" t="n">
-        <v>0</v>
-      </c>
       <c r="L57" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" t="n">
         <v>82</v>
       </c>
-      <c r="M57" t="n">
+      <c r="N57" t="n">
         <v>153</v>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>Uso oral. Fórmula infantil con ácido araquidónico, ácido docosahexaenoico y nucleótidos para bebes prematuros y/o con bajo peso al nacer de 0 a 12 meses.</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/50QWFHUpeIXibHlK0m1buSE2FvF43opN114fk1HitAo89LzRiLFh1tBaEaZw5JZSvmFmtBGltOnyXKgRpdNf7rHoCYezDts39hAChgnTL63y-RSRQg=s360-rw</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1037373-formula-infantil-similac-prematuros</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4758,40 +4969,44 @@
           <t>5099864017236</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>4.5</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="J58" t="n">
+      <c r="K58" t="n">
         <v>6</v>
       </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
       <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
         <v>86</v>
       </c>
-      <c r="M58" t="n">
+      <c r="N58" t="n">
         <v>833</v>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>La Fórmula Infantil Similac Rice está desarrollada para la alimentación de lactantes desde el nacimiento hasta los 12 meses. Su formulación está basada en proteína de arroz extensamente hidrolizada, ofreciendo una alternativa nutricional para bebés con sospecha de alergia a la proteína de leche de vaca.
 Esta fórmula especializada incluye hierro, prebiótico HMO 2-FL, nucleótidos, DHA y ARA, nutrientes que contribuyen al adecuado crecimiento y desarrollo del bebé durante el primer año de vida. Su composición nutricional permite integrarse dentro de la rutina de alimentación infantil como una opción diseñada para necesidades específicas.
@@ -4799,17 +5014,17 @@
 Alternativa para lactantes con sospecha de alergia a la proteína de leche de vaca.</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/CzMf_SXiAuOj3jwxUcFp3HXcbKhtUYb7e_SONlyY2psEi1oHGhwaFPhxkWOkkii_-JdJHhDnkXD7fvwmRywk8As7x5peMFVBbAOzk7p5pPfiCvAf=s360-rw</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/263800018-formula-infantil-similac-rice-0-12-meses-x-400-gr</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4836,56 +5051,60 @@
           <t>8427030003238</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
           <t>3.7</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
+      <c r="J59" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="J59" t="n">
+      <c r="K59" t="n">
         <v>2</v>
       </c>
-      <c r="K59" t="n">
-        <v>0</v>
-      </c>
       <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
         <v>75</v>
       </c>
-      <c r="M59" t="n">
+      <c r="N59" t="n">
         <v>396</v>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>Similac Sensitive Sin Lactosa (375 gr) es una fórmula infantil especializada a base de leche, diseñada para lactantes de 0 a 12 meses con intolerancia a la lactosa, gases, cólicos o molestias digestivas asociadas. Brinda una nutrición completa para el crecimiento y desarrollo integral del bebé mientras favorece su confort estomacal.
 Fórmula sin lactosa para necesidades especiales de nutrición</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/-hXuQwZUX1Vgo_SrdMdYwP0uRxu-Yw69_DqPI-1qGNvf4hCA6XGmvOIOUckSoBpzTrcrlOyJA7AWbmTdMLf8XL3zBa8NqO96gp9qkXGiiEacr-9x=s360-rw</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1013041-formula-infantil-similac</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4912,55 +5131,59 @@
           <t>8427030008820</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
           <t>4.3</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="J60" t="n">
+      <c r="K60" t="n">
         <v>4</v>
       </c>
-      <c r="K60" t="n">
-        <v>0</v>
-      </c>
       <c r="L60" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" t="n">
         <v>72</v>
       </c>
-      <c r="M60" t="n">
+      <c r="N60" t="n">
         <v>294</v>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>Alimento lácteo, bajo en lactosa, con proteína parcialmente hidrolizada, mezcla de grasas de fácil digestión, prebiótico HMO 2'-FL, DHA y luteína para niños de 1 a 3 años. Alimento de continuación para bebés con digestión sensible. Proteína hidrolizada que reduce gases, llanto y estreñimiento.</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/M2IFLxhoGwXPLZVpAlgyACVJSqoD9TUwqeAelQgld_GevjhvdHLome1mxdz9LM45lhDJ5jspOK8ZsNddrz41S7a9dgMIK2JWiUAxFlrNYzEqa0Ce=s360-rw</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/293350505-formula-infantil-similac-total-comfort-2-prosensitive-lata-x-820-gr</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -4987,57 +5210,61 @@
           <t>7703186032355</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J61" t="n">
+      <c r="K61" t="n">
         <v>2</v>
       </c>
-      <c r="K61" t="n">
-        <v>0</v>
-      </c>
       <c r="L61" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" t="n">
         <v>78</v>
       </c>
-      <c r="M61" t="n">
+      <c r="N61" t="n">
         <v>594</v>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>Similac Total Comfort 1 5HMO es una formula Infantil con Hierro, Proteina Parcialmente Hidrolizada, Grasas De Facil Digestión, prebioticos, 5hmos, Nucleotidos, Dha Y Luteina, Baja En Lactosa, libre de oleina de palmapara Lactantes De 0 A 12 Meses que requieren apoyo nutricional para una mejor digestión y tolerancia. Características pensadas para acompañar el bienestar digestivo de tu pequeño durante una etapa importante de crecimiento y desarrollo.
 Similac Total Comfort Kid está diseñada para apoyar una fácil digestión con menos gases y diarrea.
 Gracias a su mezcla única de nutrientes:</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/Zj0rfIQVWHZ-OKNF08UvaSfj8WegRKnBUSztFg3wuBwtNBfEIjPxElusc03X-L3eGpVMPQqBUspcRH49N5SI_AhSbbhX277GFrKaq-Vif-JHCqYr=s360-rw</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/1053211-formula-infantil-similac-etapa-1</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5064,49 +5291,51 @@
           <t>8427030009285</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="n">
+          <t>Abbott</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" t="n">
         <v>3</v>
       </c>
-      <c r="K62" t="n">
-        <v>0</v>
-      </c>
       <c r="L62" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" t="n">
         <v>71</v>
       </c>
-      <c r="M62" t="n">
+      <c r="N62" t="n">
         <v>594</v>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>Similac Total Comfort 1 5HMO es una formula Infantil con Hierro, Proteina Parcialmente Hidrolizada, Grasas De Facil Digestión, prebioticos, 5hmos, Nucleotidos, Dha Y Luteina, Baja En Lactosa, libre de oleina de palmapara Lactantes De 0 A 12 Meses que requieren apoyo nutricional para una mejor digestión y tolerancia. Características pensadas para acompañar el bienestar digestivo de tu pequeño durante una etapa importante de crecimiento y desarrollo.
 Similac Total Comfort Kid está diseñada para apoyar una fácil digestión con menos gases y diarrea.
 Gracias a su mezcla única de nutrientes:</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/aDnHhSDwCWnA155fJQ8aws1j55qZZ7RWQrV_lR3fM8jh-ShdWpZqy_hM_mRv-_iH6dXljC4zapTC1YFKBCKuERcbPMlFuAkLV6Yo7Lbswvdvc0X6jA=s360-rw</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/244800207-formula-infantil-similac-total-comfort-5hmos-etapa-1-x-800-gr</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
@@ -5133,64 +5362,68 @@
           <t>8427030009278</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Abbott</t>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>SIMILAC</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abbott</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="J63" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J63" t="n">
+      <c r="K63" t="n">
         <v>3</v>
       </c>
-      <c r="K63" t="n">
-        <v>0</v>
-      </c>
       <c r="L63" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" t="n">
         <v>71</v>
       </c>
-      <c r="M63" t="n">
+      <c r="N63" t="n">
         <v>594</v>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>Similac Total Comfort 1 5HMO es una formula Infantil con Hierro, Proteina Parcialmente Hidrolizada, Grasas De Facil Digestión, prebioticos, 5hmos, Nucleotidos, Dha Y Luteina, Baja En Lactosa, libre de oleina de palmapara Lactantes De 0 A 12 Meses que requieren apoyo nutricional para una mejor digestión y tolerancia. Características pensadas para acompañar el bienestar digestivo de tu pequeño durante una etapa importante de crecimiento y desarrollo.
 Similac Total Comfort Kid está diseñada para apoyar una fácil digestión con menos gases y diarrea.
 Gracias a su mezcla única de nutrientes:</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>https://product-images.farmatodo.com/PHhfrejrnauq_8sqtyHC6V-mcu5fHDbbbVTpzSvfDofbnydZtAQuwbHIETMGLFn083v0c-0MzfrUpHTFcZF1GNaMAoJLtHmduiBF_kVs-hOqq9I=s360-rw</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>https://www.farmatodo.com.co/producto/244750203-formula-infantil-similac-total-comfort-5hmos-etapa-1-x-350-gr</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>DISPONIBLE</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:Q63"/>
+  <autoFilter ref="A1:R63"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>